--- a/data/mortality.xlsx
+++ b/data/mortality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashuffmyer/MyProjects/oysters/manchester-hardening/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D135E93B-A74A-BA4C-836F-B9AC160F2270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0E2915-5982-4842-9525-F92CB7014DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15240" yWindow="760" windowWidth="13340" windowHeight="17380" xr2:uid="{B3863641-1C9C-E64D-B4F4-52BFC05FF521}"/>
+    <workbookView xWindow="41320" yWindow="-600" windowWidth="13340" windowHeight="17380" xr2:uid="{B3863641-1C9C-E64D-B4F4-52BFC05FF521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="13">
   <si>
     <t>tag</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>B028</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -443,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1995C9E0-0881-2F45-922C-5DDEBECC0C61}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -1333,6 +1336,826 @@
         <v>18</v>
       </c>
     </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43">
+        <v>77</v>
+      </c>
+      <c r="B43">
+        <v>20260107</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44">
+        <v>68</v>
+      </c>
+      <c r="B44">
+        <v>20260107</v>
+      </c>
+      <c r="C44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>92</v>
+      </c>
+      <c r="B45">
+        <v>20260107</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>66</v>
+      </c>
+      <c r="B46">
+        <v>20260107</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>84</v>
+      </c>
+      <c r="B47">
+        <v>20260107</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>81</v>
+      </c>
+      <c r="B48">
+        <v>20260107</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>58</v>
+      </c>
+      <c r="B49">
+        <v>20260107</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>75</v>
+      </c>
+      <c r="B50">
+        <v>20260107</v>
+      </c>
+      <c r="C50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>58</v>
+      </c>
+      <c r="B51">
+        <v>20260107</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>55</v>
+      </c>
+      <c r="B52">
+        <v>20260107</v>
+      </c>
+      <c r="C52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53">
+        <v>70</v>
+      </c>
+      <c r="B53">
+        <v>20260107</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>69</v>
+      </c>
+      <c r="B54">
+        <v>20260107</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>71</v>
+      </c>
+      <c r="B55">
+        <v>20260107</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>76</v>
+      </c>
+      <c r="B56">
+        <v>20260107</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>54</v>
+      </c>
+      <c r="B57">
+        <v>20260107</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>63</v>
+      </c>
+      <c r="B58">
+        <v>20260107</v>
+      </c>
+      <c r="C58" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>83</v>
+      </c>
+      <c r="B59">
+        <v>20260107</v>
+      </c>
+      <c r="C59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>74</v>
+      </c>
+      <c r="B60">
+        <v>20260107</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>91</v>
+      </c>
+      <c r="B61">
+        <v>20260107</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>59</v>
+      </c>
+      <c r="B62">
+        <v>20260107</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63">
+        <v>80</v>
+      </c>
+      <c r="B63">
+        <v>20260107</v>
+      </c>
+      <c r="C63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>53</v>
+      </c>
+      <c r="B64">
+        <v>20260107</v>
+      </c>
+      <c r="C64" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>20260107</v>
+      </c>
+      <c r="C65" t="s">
+        <v>10</v>
+      </c>
+      <c r="D65" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>82</v>
+      </c>
+      <c r="B66">
+        <v>20260107</v>
+      </c>
+      <c r="C66" t="s">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>88</v>
+      </c>
+      <c r="B67">
+        <v>20260107</v>
+      </c>
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+      <c r="D67" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>61</v>
+      </c>
+      <c r="B68">
+        <v>20260107</v>
+      </c>
+      <c r="C68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>72</v>
+      </c>
+      <c r="B69">
+        <v>20260107</v>
+      </c>
+      <c r="C69" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>85</v>
+      </c>
+      <c r="B70">
+        <v>20260107</v>
+      </c>
+      <c r="C70" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>67</v>
+      </c>
+      <c r="B71">
+        <v>20260107</v>
+      </c>
+      <c r="C71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>57</v>
+      </c>
+      <c r="B72">
+        <v>20260107</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72">
+        <v>2</v>
+      </c>
+      <c r="F72" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>78</v>
+      </c>
+      <c r="B73">
+        <v>20260107</v>
+      </c>
+      <c r="C73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>60</v>
+      </c>
+      <c r="B74">
+        <v>20260107</v>
+      </c>
+      <c r="C74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>87</v>
+      </c>
+      <c r="B75">
+        <v>20260107</v>
+      </c>
+      <c r="C75" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>52</v>
+      </c>
+      <c r="B76">
+        <v>20260107</v>
+      </c>
+      <c r="C76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>90</v>
+      </c>
+      <c r="B77">
+        <v>20260107</v>
+      </c>
+      <c r="C77" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>79</v>
+      </c>
+      <c r="B78">
+        <v>20260107</v>
+      </c>
+      <c r="C78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>73</v>
+      </c>
+      <c r="B79">
+        <v>20260107</v>
+      </c>
+      <c r="C79" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80">
+        <v>62</v>
+      </c>
+      <c r="B80">
+        <v>20260107</v>
+      </c>
+      <c r="C80" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81">
+        <v>65</v>
+      </c>
+      <c r="B81">
+        <v>20260107</v>
+      </c>
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82">
+        <v>56</v>
+      </c>
+      <c r="B82">
+        <v>20260107</v>
+      </c>
+      <c r="C82" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82">
+        <v>2</v>
+      </c>
+      <c r="F82" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83">
+        <v>86</v>
+      </c>
+      <c r="B83">
+        <v>20260107</v>
+      </c>
+      <c r="C83" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/mortality.xlsx
+++ b/data/mortality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashuffmyer/MyProjects/oysters/manchester-hardening/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0E2915-5982-4842-9525-F92CB7014DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AF1B30-33B4-7045-BE9E-1F4828BF16F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41320" yWindow="-600" windowWidth="13340" windowHeight="17380" xr2:uid="{B3863641-1C9C-E64D-B4F4-52BFC05FF521}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17760" xr2:uid="{B3863641-1C9C-E64D-B4F4-52BFC05FF521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="13">
   <si>
     <t>tag</t>
   </si>
@@ -446,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1995C9E0-0881-2F45-922C-5DDEBECC0C61}">
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -474,70 +474,70 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B2">
         <v>20250923</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <f>SUM(D2,E2)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B3">
         <v>20250923</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F12" si="0">SUM(D3,E3)</f>
-        <v>19</v>
+        <f>SUM(D3,E3)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="B4">
         <v>20250923</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <f>SUM(D4,E4)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B5">
         <v>20250923</v>
@@ -546,56 +546,56 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <f>SUM(D5,E5)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="B6">
         <v>20250923</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <f>SUM(D6,E6)</f>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B7">
         <v>20250923</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <f>SUM(D7,E7)</f>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -615,13 +615,13 @@
         <v>1</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
+        <f>SUM(D8,E8)</f>
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B9">
         <v>20250923</v>
@@ -630,103 +630,103 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <f>SUM(D9,E9)</f>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10">
         <v>20250923</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E10">
         <v>3</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f>SUM(D10,E10)</f>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B11">
         <v>20250923</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <f>SUM(D11,E11)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B12">
         <v>20250923</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <f t="shared" si="0"/>
-        <v>31</v>
+        <f>SUM(D12,E12)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B13">
         <v>20250923</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <f t="shared" ref="F13:F42" si="1">SUM(D13,E13)</f>
-        <v>28</v>
+        <f>SUM(D13,E13)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B14">
         <v>20250923</v>
@@ -735,484 +735,484 @@
         <v>9</v>
       </c>
       <c r="D14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f>SUM(D14,E14)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B15">
         <v>20250923</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f>SUM(D15,E15)</f>
+        <v>19</v>
+      </c>
+      <c r="G15" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B16">
         <v>20250923</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <f>SUM(D16,E16)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B17">
         <v>20250923</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17">
+        <v>14</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <f>SUM(D17,E17)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>67</v>
+      </c>
+      <c r="B18">
+        <v>20250923</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18">
+        <v>26</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <f>SUM(D18,E18)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>68</v>
+      </c>
+      <c r="B19">
+        <v>20250923</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19">
         <v>19</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <f>SUM(D19,E19)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>83</v>
-      </c>
-      <c r="B18">
-        <v>20250923</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18">
-        <v>19</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>69</v>
+      </c>
+      <c r="B20">
+        <v>20250923</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>28</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <f>SUM(D20,E20)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>70</v>
+      </c>
+      <c r="B21">
+        <v>20250923</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21">
+        <v>31</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <f>SUM(D21,E21)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>71</v>
+      </c>
+      <c r="B22">
+        <v>20250923</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22">
+        <v>14</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <f>SUM(D22,E22)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>72</v>
+      </c>
+      <c r="B23">
+        <v>20250923</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>15</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <f>SUM(D23,E23)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>73</v>
+      </c>
+      <c r="B24">
+        <v>20250923</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>14</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <f>SUM(D24,E24)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25">
         <v>74</v>
       </c>
-      <c r="B19">
-        <v>20250923</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19">
+      <c r="B25">
+        <v>20250923</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25">
         <v>21</v>
       </c>
-      <c r="E19">
+      <c r="E25">
         <v>1</v>
       </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
+      <c r="F25">
+        <f>SUM(D25,E25)</f>
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>91</v>
-      </c>
-      <c r="B20">
-        <v>20250923</v>
-      </c>
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20">
-        <v>15</v>
-      </c>
-      <c r="E20">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>75</v>
+      </c>
+      <c r="B26">
+        <v>20250923</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>21</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <f>SUM(D26,E26)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>76</v>
+      </c>
+      <c r="B27">
+        <v>20250923</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27">
+        <v>9</v>
+      </c>
+      <c r="E27">
         <v>1</v>
       </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21">
-        <v>59</v>
-      </c>
-      <c r="B21">
-        <v>20250923</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21">
-        <v>41</v>
-      </c>
-      <c r="E21">
-        <v>3</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="F27">
+        <f>SUM(D27,E27)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>77</v>
+      </c>
+      <c r="B28">
+        <v>20250923</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>13</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <f>SUM(D28,E28)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>78</v>
+      </c>
+      <c r="B29">
+        <v>20250923</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29">
+        <v>10</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <f>SUM(D29,E29)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>79</v>
+      </c>
+      <c r="B30">
+        <v>20250923</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>12</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <f>SUM(D30,E30)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31">
         <v>80</v>
       </c>
-      <c r="B22">
-        <v>20250923</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22">
+      <c r="B31">
+        <v>20250923</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31">
         <v>38</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <f>SUM(D31,E31)</f>
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23">
-        <v>53</v>
-      </c>
-      <c r="B23">
-        <v>20250923</v>
-      </c>
-      <c r="C23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D23">
-        <v>23</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>64</v>
-      </c>
-      <c r="B24">
-        <v>20250923</v>
-      </c>
-      <c r="C24" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24">
-        <v>18</v>
-      </c>
-      <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="G24" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25">
-        <v>82</v>
-      </c>
-      <c r="B25">
-        <v>20250923</v>
-      </c>
-      <c r="C25" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25">
-        <v>37</v>
-      </c>
-      <c r="E25">
-        <v>3</v>
-      </c>
-      <c r="F25">
-        <f t="shared" si="1"/>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>81</v>
+      </c>
+      <c r="B32">
+        <v>20250923</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32">
         <v>40</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>88</v>
-      </c>
-      <c r="B26">
-        <v>20250923</v>
-      </c>
-      <c r="C26" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26">
-        <v>15</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>61</v>
-      </c>
-      <c r="B27">
-        <v>20250923</v>
-      </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27">
-        <v>23</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>72</v>
-      </c>
-      <c r="B28">
-        <v>20250923</v>
-      </c>
-      <c r="C28" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28">
-        <v>15</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>85</v>
-      </c>
-      <c r="B29">
-        <v>20250923</v>
-      </c>
-      <c r="C29" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29">
-        <v>19</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>67</v>
-      </c>
-      <c r="B30">
-        <v>20250923</v>
-      </c>
-      <c r="C30" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30">
-        <v>26</v>
-      </c>
-      <c r="E30">
-        <v>1</v>
-      </c>
-      <c r="F30">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>57</v>
-      </c>
-      <c r="B31">
-        <v>20250923</v>
-      </c>
-      <c r="C31" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31">
-        <v>45</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <f t="shared" si="1"/>
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>78</v>
-      </c>
-      <c r="B32">
-        <v>20250923</v>
-      </c>
-      <c r="C32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32">
-        <v>10</v>
-      </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <f t="shared" si="1"/>
-        <v>11</v>
+        <f>SUM(D32,E32)</f>
+        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B33">
         <v>20250923</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <f t="shared" si="1"/>
-        <v>17</v>
+        <f>SUM(D33,E33)</f>
+        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B34">
         <v>20250923</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D34">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <f>SUM(D34,E34)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B35">
         <v>20250923</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D35">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="F35">
-        <f t="shared" si="1"/>
-        <v>18</v>
+        <f>SUM(D35,E35)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B36">
         <v>20250923</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="F36">
-        <f t="shared" si="1"/>
-        <v>38</v>
+        <f>SUM(D36,E36)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B37">
         <v>20250923</v>
@@ -1221,19 +1221,19 @@
         <v>11</v>
       </c>
       <c r="D37">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <f>SUM(D37,E37)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B38">
         <v>20250923</v>
@@ -1242,40 +1242,40 @@
         <v>11</v>
       </c>
       <c r="D38">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <f t="shared" si="1"/>
+        <f>SUM(D38,E38)</f>
         <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B39">
         <v>20250923</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <f t="shared" si="1"/>
-        <v>23</v>
+        <f>SUM(D39,E39)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B40">
         <v>20250923</v>
@@ -1284,67 +1284,67 @@
         <v>11</v>
       </c>
       <c r="D40">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <f t="shared" si="1"/>
-        <v>29</v>
+        <f>SUM(D40,E40)</f>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B41">
         <v>20250923</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D41">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E41">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <f t="shared" si="1"/>
-        <v>48</v>
+        <f>SUM(D41,E41)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B42">
         <v>20250923</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D42">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <f t="shared" si="1"/>
-        <v>18</v>
+        <f>SUM(D42,E42)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B43">
         <v>20260107</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D43" t="s">
         <v>12</v>
@@ -1358,13 +1358,13 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B44">
         <v>20260107</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D44" t="s">
         <v>12</v>
@@ -1378,13 +1378,13 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="B45">
         <v>20260107</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" t="s">
         <v>12</v>
@@ -1398,7 +1398,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B46">
         <v>20260107</v>
@@ -1418,19 +1418,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="B47">
         <v>20260107</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D47" t="s">
         <v>12</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F47" t="s">
         <v>12</v>
@@ -1438,19 +1438,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="B48">
         <v>20260107</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D48" t="s">
         <v>12</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" t="s">
         <v>12</v>
@@ -1478,7 +1478,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B50">
         <v>20260107</v>
@@ -1498,13 +1498,13 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B51">
         <v>20260107</v>
       </c>
       <c r="C51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
@@ -1518,13 +1518,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B52">
         <v>20260107</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D52" t="s">
         <v>12</v>
@@ -1538,19 +1538,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="B53">
         <v>20260107</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D53" t="s">
         <v>12</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="s">
         <v>12</v>
@@ -1558,19 +1558,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B54">
         <v>20260107</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D54" t="s">
         <v>12</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F54" t="s">
         <v>12</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B55">
         <v>20260107</v>
@@ -1598,13 +1598,13 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B56">
         <v>20260107</v>
       </c>
       <c r="C56" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D56" t="s">
         <v>12</v>
@@ -1618,13 +1618,13 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="B57">
         <v>20260107</v>
       </c>
       <c r="C57" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D57" t="s">
         <v>12</v>
@@ -1638,13 +1638,13 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B58">
         <v>20260107</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D58" t="s">
         <v>12</v>
@@ -1658,19 +1658,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="B59">
         <v>20260107</v>
       </c>
       <c r="C59" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D59" t="s">
         <v>12</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="s">
         <v>12</v>
@@ -1678,13 +1678,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B60">
         <v>20260107</v>
       </c>
       <c r="C60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D60" t="s">
         <v>12</v>
@@ -1698,7 +1698,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B61">
         <v>20260107</v>
@@ -1710,7 +1710,7 @@
         <v>12</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="s">
         <v>12</v>
@@ -1718,19 +1718,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="B62">
         <v>20260107</v>
       </c>
       <c r="C62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" t="s">
         <v>12</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
@@ -1738,7 +1738,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="B63">
         <v>20260107</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="B64">
         <v>20260107</v>
@@ -1778,19 +1778,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B65">
         <v>20260107</v>
       </c>
       <c r="C65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D65" t="s">
         <v>12</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="s">
         <v>12</v>
@@ -1798,13 +1798,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B66">
         <v>20260107</v>
       </c>
       <c r="C66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D66" t="s">
         <v>12</v>
@@ -1818,19 +1818,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B67">
         <v>20260107</v>
       </c>
       <c r="C67" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D67" t="s">
         <v>12</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B68">
         <v>20260107</v>
       </c>
       <c r="C68" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D68" t="s">
         <v>12</v>
@@ -1858,13 +1858,13 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B69">
         <v>20260107</v>
       </c>
       <c r="C69" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D69" t="s">
         <v>12</v>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B70">
         <v>20260107</v>
@@ -1898,13 +1898,13 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B71">
         <v>20260107</v>
       </c>
       <c r="C71" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D71" t="s">
         <v>12</v>
@@ -1918,19 +1918,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B72">
         <v>20260107</v>
       </c>
       <c r="C72" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D72" t="s">
         <v>12</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" t="s">
         <v>12</v>
@@ -1938,13 +1938,13 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B73">
         <v>20260107</v>
       </c>
       <c r="C73" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D73" t="s">
         <v>12</v>
@@ -1958,13 +1958,13 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B74">
         <v>20260107</v>
       </c>
       <c r="C74" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D74" t="s">
         <v>12</v>
@@ -1978,19 +1978,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B75">
         <v>20260107</v>
       </c>
       <c r="C75" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D75" t="s">
         <v>12</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="s">
         <v>12</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="B76">
         <v>20260107</v>
       </c>
       <c r="C76" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D76" t="s">
         <v>12</v>
@@ -2018,13 +2018,13 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B77">
         <v>20260107</v>
       </c>
       <c r="C77" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D77" t="s">
         <v>12</v>
@@ -2038,7 +2038,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B78">
         <v>20260107</v>
@@ -2058,7 +2058,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="B79">
         <v>20260107</v>
@@ -2070,7 +2070,7 @@
         <v>12</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" t="s">
         <v>12</v>
@@ -2078,19 +2078,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B80">
         <v>20260107</v>
       </c>
       <c r="C80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D80" t="s">
         <v>12</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F80" t="s">
         <v>12</v>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B81">
         <v>20260107</v>
@@ -2118,19 +2118,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B82">
         <v>20260107</v>
       </c>
       <c r="C82" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D82" t="s">
         <v>12</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F82" t="s">
         <v>12</v>
@@ -2138,25 +2138,849 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83">
+        <v>92</v>
+      </c>
+      <c r="B83">
+        <v>20260107</v>
+      </c>
+      <c r="C83" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84">
+        <v>52</v>
+      </c>
+      <c r="B84">
+        <v>20260528</v>
+      </c>
+      <c r="C84" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85">
+        <v>53</v>
+      </c>
+      <c r="B85">
+        <v>20260528</v>
+      </c>
+      <c r="C85" t="s">
+        <v>10</v>
+      </c>
+      <c r="D85" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86">
+        <v>54</v>
+      </c>
+      <c r="B86">
+        <v>20260528</v>
+      </c>
+      <c r="C86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87">
+        <v>55</v>
+      </c>
+      <c r="B87">
+        <v>20260528</v>
+      </c>
+      <c r="C87" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88">
+        <v>56</v>
+      </c>
+      <c r="B88">
+        <v>20260528</v>
+      </c>
+      <c r="C88" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89">
+        <v>57</v>
+      </c>
+      <c r="B89">
+        <v>20260528</v>
+      </c>
+      <c r="C89" t="s">
+        <v>10</v>
+      </c>
+      <c r="D89" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90">
+        <v>58</v>
+      </c>
+      <c r="B90">
+        <v>20260528</v>
+      </c>
+      <c r="C90" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91">
+        <v>58</v>
+      </c>
+      <c r="B91">
+        <v>20260528</v>
+      </c>
+      <c r="C91" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92">
+        <v>59</v>
+      </c>
+      <c r="B92">
+        <v>20260528</v>
+      </c>
+      <c r="C92" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93">
+        <v>60</v>
+      </c>
+      <c r="B93">
+        <v>20260528</v>
+      </c>
+      <c r="C93" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94">
+        <v>61</v>
+      </c>
+      <c r="B94">
+        <v>20260528</v>
+      </c>
+      <c r="C94" t="s">
+        <v>10</v>
+      </c>
+      <c r="D94" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95">
+        <v>62</v>
+      </c>
+      <c r="B95">
+        <v>20260528</v>
+      </c>
+      <c r="C95" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>63</v>
+      </c>
+      <c r="B96">
+        <v>20260528</v>
+      </c>
+      <c r="C96" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>64</v>
+      </c>
+      <c r="B97">
+        <v>20260528</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>65</v>
+      </c>
+      <c r="B98">
+        <v>20260528</v>
+      </c>
+      <c r="C98" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>66</v>
+      </c>
+      <c r="B99">
+        <v>20260528</v>
+      </c>
+      <c r="C99" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>67</v>
+      </c>
+      <c r="B100">
+        <v>20260528</v>
+      </c>
+      <c r="C100" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>68</v>
+      </c>
+      <c r="B101">
+        <v>20260528</v>
+      </c>
+      <c r="C101" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>69</v>
+      </c>
+      <c r="B102">
+        <v>20260528</v>
+      </c>
+      <c r="C102" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>70</v>
+      </c>
+      <c r="B103">
+        <v>20260528</v>
+      </c>
+      <c r="C103" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>71</v>
+      </c>
+      <c r="B104">
+        <v>20260528</v>
+      </c>
+      <c r="C104" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>72</v>
+      </c>
+      <c r="B105">
+        <v>20260528</v>
+      </c>
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105" t="s">
+        <v>12</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>73</v>
+      </c>
+      <c r="B106">
+        <v>20260528</v>
+      </c>
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>74</v>
+      </c>
+      <c r="B107">
+        <v>20260528</v>
+      </c>
+      <c r="C107" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
+      <c r="F107" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>75</v>
+      </c>
+      <c r="B108">
+        <v>20260528</v>
+      </c>
+      <c r="C108" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>76</v>
+      </c>
+      <c r="B109">
+        <v>20260528</v>
+      </c>
+      <c r="C109" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" t="s">
+        <v>12</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>77</v>
+      </c>
+      <c r="B110">
+        <v>20260528</v>
+      </c>
+      <c r="C110" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+      <c r="F110" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>78</v>
+      </c>
+      <c r="B111">
+        <v>20260528</v>
+      </c>
+      <c r="C111" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>79</v>
+      </c>
+      <c r="B112">
+        <v>20260528</v>
+      </c>
+      <c r="C112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>80</v>
+      </c>
+      <c r="B113">
+        <v>20260528</v>
+      </c>
+      <c r="C113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
+      </c>
+      <c r="F113" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>81</v>
+      </c>
+      <c r="B114">
+        <v>20260528</v>
+      </c>
+      <c r="C114" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>82</v>
+      </c>
+      <c r="B115">
+        <v>20260528</v>
+      </c>
+      <c r="C115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115">
+        <v>1</v>
+      </c>
+      <c r="F115" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>83</v>
+      </c>
+      <c r="B116">
+        <v>20260528</v>
+      </c>
+      <c r="C116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116">
+        <v>2</v>
+      </c>
+      <c r="F116" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>84</v>
+      </c>
+      <c r="B117">
+        <v>20260528</v>
+      </c>
+      <c r="C117" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>85</v>
+      </c>
+      <c r="B118">
+        <v>20260528</v>
+      </c>
+      <c r="C118" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119">
         <v>86</v>
       </c>
-      <c r="B83">
-        <v>20260107</v>
-      </c>
-      <c r="C83" t="s">
-        <v>11</v>
-      </c>
-      <c r="D83" t="s">
-        <v>12</v>
-      </c>
-      <c r="E83">
-        <v>0</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="B119">
+        <v>20260528</v>
+      </c>
+      <c r="C119" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>87</v>
+      </c>
+      <c r="B120">
+        <v>20260528</v>
+      </c>
+      <c r="C120" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" t="s">
+        <v>12</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>88</v>
+      </c>
+      <c r="B121">
+        <v>20260528</v>
+      </c>
+      <c r="C121" t="s">
+        <v>10</v>
+      </c>
+      <c r="D121" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>90</v>
+      </c>
+      <c r="B122">
+        <v>20260528</v>
+      </c>
+      <c r="C122" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" t="s">
+        <v>12</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
+      </c>
+      <c r="F122" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>91</v>
+      </c>
+      <c r="B123">
+        <v>20260528</v>
+      </c>
+      <c r="C123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" t="s">
+        <v>12</v>
+      </c>
+      <c r="E123">
+        <v>1</v>
+      </c>
+      <c r="F123" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>92</v>
+      </c>
+      <c r="B124">
+        <v>20260528</v>
+      </c>
+      <c r="C124" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G124">
+    <sortCondition ref="B2:B124"/>
+    <sortCondition ref="A2:A124"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>